--- a/output/pdf_financials_xlsx/SWLF.xlsx
+++ b/output/pdf_financials_xlsx/SWLF.xlsx
@@ -7001,34 +7001,34 @@
         <v>-0.0005</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004583</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.006119</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>1.898399</v>
+        <v>1.58336</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004409</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.650238</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.597824</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.250577</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.903931</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.200766</v>
       </c>
     </row>
     <row r="119">
@@ -9964,7 +9964,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -20278,7 +20282,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SWLF.xlsx
+++ b/output/pdf_financials_xlsx/SWLF.xlsx
@@ -999,28 +999,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.010676</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001767</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1924,28 +1924,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.107673</v>
+        <v>-0.118349</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.392672</v>
+        <v>-0.394439</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.222806</v>
+        <v>-0.222814</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.118932</v>
+        <v>-0.118951</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.05467</v>
+        <v>-0.05469</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.06514300000000001</v>
+        <v>-0.06515799999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.054926</v>
+        <v>-0.054956</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.060766</v>
+        <v>-0.06081</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.010978</v>
@@ -2034,28 +2034,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.107673</v>
+        <v>-0.118349</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.392672</v>
+        <v>-0.394439</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.222806</v>
+        <v>-0.222814</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.118932</v>
+        <v>-0.118951</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.05467</v>
+        <v>-0.05469</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.06514300000000001</v>
+        <v>-0.06515799999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.054926</v>
+        <v>-0.054956</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.060766</v>
+        <v>-0.06081</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.010978</v>
@@ -2337,31 +2337,31 @@
         <v>0.164002</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.037037</v>
+        <v>0.005773</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.005561</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00247</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005759</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.051287</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.131207</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.026027</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.364784</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.208715</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.059221</v>
@@ -2447,31 +2447,31 @@
         <v>0.164002</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.051534</v>
+        <v>0.02027</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.005561</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.00247</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005759</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.051287</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.131207</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.026027</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.364784</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.208715</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.059221</v>
@@ -3110,28 +3110,28 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.005561</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00247</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.005759</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.051287</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.144308</v>
+        <v>0.013101</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.029231</v>
+        <v>0.003204</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.42314</v>
+        <v>0.058356</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.224131</v>
+        <v>0.015416</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -7343,22 +7343,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.00735</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016739</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014118</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009186</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.006999</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005018</v>
       </c>
     </row>
     <row r="125">
@@ -7398,22 +7398,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.00735</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016739</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014118</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009186</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.006999</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005018</v>
       </c>
     </row>
     <row r="126">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10234,7 +10234,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11264,7 +11268,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12378,7 +12386,11 @@
           <t>Reclamation Deposit 7</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -13150,7 +13162,11 @@
           <t>Reclamation Deposit 6</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -13996,7 +14012,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15060,7 +15080,11 @@
           <t>Reclamation deposit 6 3,000</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -20522,7 +20546,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -36746,7 +36774,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -39014,7 +39042,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -41680,7 +41708,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -43108,7 +43136,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" s="5" t="n">

--- a/output/pdf_financials_xlsx/SWLF.xlsx
+++ b/output/pdf_financials_xlsx/SWLF.xlsx
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.012501</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.000711</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -30358,7 +30358,11 @@
           <t>- GST recoverable</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E238" s="5" t="n">
         <v>0.012501</v>
       </c>
